--- a/examples/edm_teste_campinas.xlsx
+++ b/examples/edm_teste_campinas.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e Campinas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,11 +30,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,22 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00595959"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,22 +66,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -636,109 +617,16 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="4" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>01/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Serviços de consultoria em tecnologia da informação</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Empresa Tomadora Ltda</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>12.345.678/0001-90</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>financeiro@empresa.com.br</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Rua Exemplo</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>Sala 5</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>13010100</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>3509502</t>
-        </is>
-      </c>
-      <c r="R2" s="4" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>04/2026</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Honorários Contábeis - Prestacao de servico em contabilidade
 Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
@@ -746,299 +634,82 @@
 Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>17.19</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E2" t="n">
         <v>450</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>18.298.204/0001-16</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>ericmaubr@gmail.com</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>R SALDANHA DA GAMA</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr"/>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>LAPA</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>05081000</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>3550308</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>6920601</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>INSTRUÇÕES DE PREENCHIMENTO — NFS-e CAMPINAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>CAMPOS OBRIGATÓRIOS (marcados com *)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>numero_rps        Número sequencial do RPS. Cada linha deve ter um número único.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>competencia       Mês/ano de competência no formato MM/AAAA. Exemplo: 01/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>discriminacao     Descrição completa do serviço prestado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>codigo_servico    Código LC 116/2003. Exemplos: 1.07 (informática), 17.01 (assessoria).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>valor_servico     Valor dos serviços em reais. Use ponto como separador decimal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tomador_razao_social  Nome ou razão social do tomador (cliente final).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tomador_cnpj      CNPJ do tomador (pessoa jurídica). OU</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tomador_cpf       CPF do tomador (pessoa física). Preencha um dos dois.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>CAMPOS OPCIONAIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>data_emissao      Data de emissão no formato DD/MM/AAAA. Se vazio, usa a data de hoje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>iss_retido        ISS retido na fonte? S ou N. Default: N</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>optante_simples   Tomador é optante pelo Simples Nacional? S ou N. Default: N</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>deducoes          Valor das deduções em reais. Default: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>natureza_operacao 1=Tributação no município (default), 2=Fora do município</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>RESULTADO (preenchido automaticamente após emissão)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>status            EMITIDA ou ERRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>numero_nfse       Número da NFS-e emitida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>codigo_verificacao  Código de verificação para consulta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>link_consulta     URL para visualização/download da nota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>erro              Mensagem de erro, se houver.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>DICAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>- Mantenha a linha 1 (cabeçalho) sem alterações.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>- A linha 2 é apenas um exemplo; substitua pelos dados reais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>- Adicione uma linha por nota fiscal a emitir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>- Código IBGE de Campinas: 3509502</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>- Códigos de serviço: consulte o ISS Campinas para o código municipal correto.</t>
         </is>
       </c>
     </row>

--- a/examples/edm_teste_campinas.xlsx
+++ b/examples/edm_teste_campinas.xlsx
@@ -1,178 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\conta-tools-nfse\examples\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43873611-6F84-4173-BB3A-121B01C0DBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NFS-e Campinas" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e Campinas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Número RPS *</t>
-  </si>
-  <si>
-    <t>Competência (MM/AAAA) *</t>
-  </si>
-  <si>
-    <t>Discriminação do Serviço *</t>
-  </si>
-  <si>
-    <t>Código do Serviço *</t>
-  </si>
-  <si>
-    <t>Valor dos Serviços (R$) *</t>
-  </si>
-  <si>
-    <t>Razão Social do Tomador *</t>
-  </si>
-  <si>
-    <t>CNPJ do Tomador *</t>
-  </si>
-  <si>
-    <t>CPF do Tomador (PF) *</t>
-  </si>
-  <si>
-    <t>Data de Emissão (DD/MM/AAAA)</t>
-  </si>
-  <si>
-    <t>Inscrição Municipal do Tomador</t>
-  </si>
-  <si>
-    <t>E-mail do Tomador</t>
-  </si>
-  <si>
-    <t>Logradouro do Tomador</t>
-  </si>
-  <si>
-    <t>Número do Endereço</t>
-  </si>
-  <si>
-    <t>Complemento</t>
-  </si>
-  <si>
-    <t>Bairro do Tomador</t>
-  </si>
-  <si>
-    <t>CEP do Tomador (somente dígitos)</t>
-  </si>
-  <si>
-    <t>Código IBGE do Município do Tomador</t>
-  </si>
-  <si>
-    <t>UF do Tomador</t>
-  </si>
-  <si>
-    <t>Deduções (R$)</t>
-  </si>
-  <si>
-    <t>ISS Retido? (S/N)</t>
-  </si>
-  <si>
-    <t>Optante Simples Nacional? (S/N)</t>
-  </si>
-  <si>
-    <t>Natureza Operação (1=Município, 2=Fora)</t>
-  </si>
-  <si>
-    <t>Código CNAE</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Número NFS-e</t>
-  </si>
-  <si>
-    <t>Código Verificação</t>
-  </si>
-  <si>
-    <t>Link Consulta</t>
-  </si>
-  <si>
-    <t>Mensagem de Erro</t>
-  </si>
-  <si>
-    <t>Honorários Contábeis - Prestacao de servico em contabilidade
-Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
-Honorários Contábeis - Prestacao de servicos Fiscais
-Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
-  </si>
-  <si>
-    <t>17.19</t>
-  </si>
-  <si>
-    <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
-  </si>
-  <si>
-    <t>18.298.204/0001-16</t>
-  </si>
-  <si>
-    <t>ericmaubr@gmail.com</t>
-  </si>
-  <si>
-    <t>R SALDANHA DA GAMA</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>LAPA</t>
-  </si>
-  <si>
-    <t>05081000</t>
-  </si>
-  <si>
-    <t>3550308</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>6920601</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -206,31 +67,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -518,176 +438,267 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="12" width="32" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="22" width="22" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="28" width="18" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Número RPS *</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Competência (MM/AAAA) *</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Discriminação do Serviço *</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Código do Serviço *</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor dos Serviços (R$) *</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Razão Social do Tomador *</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CNPJ do Tomador *</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CPF do Tomador (PF) *</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Data de Emissão (DD/MM/AAAA)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Inscrição Municipal do Tomador</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>E-mail do Tomador</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Logradouro do Tomador</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Número do Endereço</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Bairro do Tomador</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>CEP do Tomador (somente dígitos)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Código IBGE do Município do Tomador</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>UF do Tomador</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Deduções (R$)</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>ISS Retido? (S/N)</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Optante Simples Nacional? (S/N)</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Natureza Operação (1=Município, 2=Fora)</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Código CNAE</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Número NFS-e</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Código Verificação</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Link Consulta</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>Mensagem de Erro</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12752</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Honorários Contábeis - Prestacao de servico em contabilidade
+Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
+Honorários Contábeis - Prestacao de servicos Fiscais
+Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17.19</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>450</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>18.298.204/0001-16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ericmaubr@gmail.com</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>R SALDANHA DA GAMA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LAPA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>05081000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3550308</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>12750</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46174</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2">
-        <v>450</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2" t="s">
-        <v>41</v>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>6920601</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/examples/edm_teste_campinas.xlsx
+++ b/examples/edm_teste_campinas.xlsx
@@ -1,39 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\conta-tools-nfse\examples\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB67018-DD2E-4762-9691-98F01204E5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e Campinas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NFS-e Campinas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+  <si>
+    <t>Número RPS *</t>
+  </si>
+  <si>
+    <t>Competência (MM/AAAA) *</t>
+  </si>
+  <si>
+    <t>Discriminação do Serviço *</t>
+  </si>
+  <si>
+    <t>Código do Serviço *</t>
+  </si>
+  <si>
+    <t>Valor dos Serviços (R$) *</t>
+  </si>
+  <si>
+    <t>Razão Social do Tomador *</t>
+  </si>
+  <si>
+    <t>CNPJ do Tomador *</t>
+  </si>
+  <si>
+    <t>CPF do Tomador (PF) *</t>
+  </si>
+  <si>
+    <t>Data de Emissão (DD/MM/AAAA)</t>
+  </si>
+  <si>
+    <t>Inscrição Municipal do Tomador</t>
+  </si>
+  <si>
+    <t>E-mail do Tomador</t>
+  </si>
+  <si>
+    <t>Logradouro do Tomador</t>
+  </si>
+  <si>
+    <t>Número do Endereço</t>
+  </si>
+  <si>
+    <t>Complemento</t>
+  </si>
+  <si>
+    <t>Bairro do Tomador</t>
+  </si>
+  <si>
+    <t>CEP do Tomador (somente dígitos)</t>
+  </si>
+  <si>
+    <t>Código IBGE do Município do Tomador</t>
+  </si>
+  <si>
+    <t>UF do Tomador</t>
+  </si>
+  <si>
+    <t>Deduções (R$)</t>
+  </si>
+  <si>
+    <t>ISS Retido? (S/N)</t>
+  </si>
+  <si>
+    <t>Optante Simples Nacional? (S/N)</t>
+  </si>
+  <si>
+    <t>Natureza Operação (1=Município, 2=Fora)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Número NFS-e</t>
+  </si>
+  <si>
+    <t>Código Verificação</t>
+  </si>
+  <si>
+    <t>Link Consulta</t>
+  </si>
+  <si>
+    <t>Mensagem de Erro</t>
+  </si>
+  <si>
+    <t>Honorários Contábeis - Prestacao de servico em contabilidade
+Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
+Honorários Contábeis - Prestacao de servicos Fiscais
+Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
+  </si>
+  <si>
+    <t>17.19</t>
+  </si>
+  <si>
+    <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
+  </si>
+  <si>
+    <t>18.298.204/0001-16</t>
+  </si>
+  <si>
+    <t>ericmaubr@gmail.com</t>
+  </si>
+  <si>
+    <t>R SALDANHA DA GAMA</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>LAPA</t>
+  </si>
+  <si>
+    <t>05081000</t>
+  </si>
+  <si>
+    <t>3550308</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Código CNAE (7 ou 9 dígitos)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -67,90 +201,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -438,267 +513,176 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="28"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="12" width="32" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="24" max="28" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Número RPS *</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Competência (MM/AAAA) *</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Discriminação do Serviço *</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Código do Serviço *</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Valor dos Serviços (R$) *</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Razão Social do Tomador *</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>CNPJ do Tomador *</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CPF do Tomador (PF) *</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Data de Emissão (DD/MM/AAAA)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Inscrição Municipal do Tomador</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>E-mail do Tomador</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Logradouro do Tomador</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Número do Endereço</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Complemento</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Bairro do Tomador</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>CEP do Tomador (somente dígitos)</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Código IBGE do Município do Tomador</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>UF do Tomador</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>Deduções (R$)</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>ISS Retido? (S/N)</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>Optante Simples Nacional? (S/N)</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>Natureza Operação (1=Município, 2=Fora)</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>Código CNAE</t>
-        </is>
-      </c>
-      <c r="X1" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Y1" s="3" t="inlineStr">
-        <is>
-          <t>Número NFS-e</t>
-        </is>
-      </c>
-      <c r="Z1" s="3" t="inlineStr">
-        <is>
-          <t>Código Verificação</t>
-        </is>
-      </c>
-      <c r="AA1" s="3" t="inlineStr">
-        <is>
-          <t>Link Consulta</t>
-        </is>
-      </c>
-      <c r="AB1" s="3" t="inlineStr">
-        <is>
-          <t>Mensagem de Erro</t>
-        </is>
+    <row r="1" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>12752</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4">
         <v>46174</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Honorários Contábeis - Prestacao de servico em contabilidade
-Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
-Honorários Contábeis - Prestacao de servicos Fiscais
-Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>17.19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2">
         <v>450</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>18.298.204/0001-16</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ericmaubr@gmail.com</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>R SALDANHA DA GAMA</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>LAPA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>05081000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3550308</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
+      <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2">
         <v>1</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>6920601</t>
-        </is>
+      <c r="W2">
+        <v>692060100</v>
       </c>
     </row>
   </sheetData>

--- a/examples/edm_teste_campinas.xlsx
+++ b/examples/edm_teste_campinas.xlsx
@@ -1,173 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\conta-tools-nfse\examples\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB67018-DD2E-4762-9691-98F01204E5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NFS-e Campinas" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFS-e Campinas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
-  <si>
-    <t>Número RPS *</t>
-  </si>
-  <si>
-    <t>Competência (MM/AAAA) *</t>
-  </si>
-  <si>
-    <t>Discriminação do Serviço *</t>
-  </si>
-  <si>
-    <t>Código do Serviço *</t>
-  </si>
-  <si>
-    <t>Valor dos Serviços (R$) *</t>
-  </si>
-  <si>
-    <t>Razão Social do Tomador *</t>
-  </si>
-  <si>
-    <t>CNPJ do Tomador *</t>
-  </si>
-  <si>
-    <t>CPF do Tomador (PF) *</t>
-  </si>
-  <si>
-    <t>Data de Emissão (DD/MM/AAAA)</t>
-  </si>
-  <si>
-    <t>Inscrição Municipal do Tomador</t>
-  </si>
-  <si>
-    <t>E-mail do Tomador</t>
-  </si>
-  <si>
-    <t>Logradouro do Tomador</t>
-  </si>
-  <si>
-    <t>Número do Endereço</t>
-  </si>
-  <si>
-    <t>Complemento</t>
-  </si>
-  <si>
-    <t>Bairro do Tomador</t>
-  </si>
-  <si>
-    <t>CEP do Tomador (somente dígitos)</t>
-  </si>
-  <si>
-    <t>Código IBGE do Município do Tomador</t>
-  </si>
-  <si>
-    <t>UF do Tomador</t>
-  </si>
-  <si>
-    <t>Deduções (R$)</t>
-  </si>
-  <si>
-    <t>ISS Retido? (S/N)</t>
-  </si>
-  <si>
-    <t>Optante Simples Nacional? (S/N)</t>
-  </si>
-  <si>
-    <t>Natureza Operação (1=Município, 2=Fora)</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Número NFS-e</t>
-  </si>
-  <si>
-    <t>Código Verificação</t>
-  </si>
-  <si>
-    <t>Link Consulta</t>
-  </si>
-  <si>
-    <t>Mensagem de Erro</t>
-  </si>
-  <si>
-    <t>Honorários Contábeis - Prestacao de servico em contabilidade
-Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
-Honorários Contábeis - Prestacao de servicos Fiscais
-Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
-  </si>
-  <si>
-    <t>17.19</t>
-  </si>
-  <si>
-    <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
-  </si>
-  <si>
-    <t>18.298.204/0001-16</t>
-  </si>
-  <si>
-    <t>ericmaubr@gmail.com</t>
-  </si>
-  <si>
-    <t>R SALDANHA DA GAMA</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>LAPA</t>
-  </si>
-  <si>
-    <t>05081000</t>
-  </si>
-  <si>
-    <t>3550308</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Código CNAE (7 ou 9 dígitos)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -201,31 +68,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -513,175 +439,264 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="12" width="32" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="22" width="22" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="28" width="18" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Número RPS *</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Competência (MM/AAAA) *</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Discriminação do Serviço *</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Código do Serviço *</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor dos Serviços (R$) *</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Razão Social do Tomador *</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CNPJ do Tomador *</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CPF do Tomador (PF) *</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Data de Emissão (DD/MM/AAAA)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Inscrição Municipal do Tomador</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>E-mail do Tomador</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Logradouro do Tomador</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Número do Endereço</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Complemento</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Bairro do Tomador</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>CEP do Tomador (somente dígitos)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Código IBGE do Município do Tomador</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>UF do Tomador</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Deduções (R$)</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>ISS Retido? (S/N)</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Optante Simples Nacional? (S/N)</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Natureza Operação (1=Município, 2=Fora)</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Código CNAE (7 ou 9 dígitos)</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Número NFS-e</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Código Verificação</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Link Consulta</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>Mensagem de Erro</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Honorários Contábeis - Prestacao de servico em contabilidade
+Honorários Contábeis - Prestacao de servicos de Departamento Pessoal
+Honorários Contábeis - Prestacao de servicos Fiscais
+Contrato N. 2025/00103 - Ref. Abr/2026 - Vencto. 15/05/2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17.19</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>450</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EDM ASSESSORIA ADMINISTRATIVA E TECNOLOGICA EIRELI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>18.298.204/0001-16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ericmaubr@gmail.com</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>R SALDANHA DA GAMA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LAPA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>05081000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3550308</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>12752</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46174</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2">
-        <v>450</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2">
+      <c r="W2" t="n">
         <v>692060100</v>
       </c>
     </row>
